--- a/regions.xlsx
+++ b/regions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10411"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aleksandr/PycharmProjects/Competitions_TT_SQL/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alex\Competitions_TT_AI_v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1159937-7FE4-3146-A38A-9B442DEB2566}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A3F711-48DA-4E49-BD79-E6D6A0D362E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5180" yWindow="1900" windowWidth="28040" windowHeight="17360" xr2:uid="{D6AC9D0F-EFD6-6F43-82B0-0C9378ED95C5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D6AC9D0F-EFD6-6F43-82B0-0C9378ED95C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
   <si>
     <t>г. Москва</t>
   </si>
@@ -280,6 +280,15 @@
   </si>
   <si>
     <t>ЯНАО</t>
+  </si>
+  <si>
+    <t>ДНР</t>
+  </si>
+  <si>
+    <t>ЛНР</t>
+  </si>
+  <si>
+    <t>Херсонская обл.</t>
   </si>
 </sst>
 </file>
@@ -640,13 +649,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB559B66-8EA6-1341-B13D-F8286F6F462E}">
-  <dimension ref="A1:B85"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:B88"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="62" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A1" s="1">
         <v>1</v>
       </c>
@@ -654,7 +663,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>2</v>
       </c>
@@ -662,7 +671,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>3</v>
       </c>
@@ -670,7 +679,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>4</v>
       </c>
@@ -678,7 +687,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>5</v>
       </c>
@@ -686,7 +695,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>6</v>
       </c>
@@ -694,7 +703,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>7</v>
       </c>
@@ -702,7 +711,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>8</v>
       </c>
@@ -710,7 +719,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>9</v>
       </c>
@@ -718,7 +727,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>10</v>
       </c>
@@ -726,7 +735,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>11</v>
       </c>
@@ -734,7 +743,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>12</v>
       </c>
@@ -742,7 +751,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>13</v>
       </c>
@@ -750,7 +759,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>14</v>
       </c>
@@ -758,7 +767,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>15</v>
       </c>
@@ -766,7 +775,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>16</v>
       </c>
@@ -774,7 +783,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>17</v>
       </c>
@@ -782,7 +791,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>18</v>
       </c>
@@ -790,7 +799,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>19</v>
       </c>
@@ -798,7 +807,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>20</v>
       </c>
@@ -806,7 +815,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>21</v>
       </c>
@@ -814,7 +823,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>22</v>
       </c>
@@ -822,7 +831,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>23</v>
       </c>
@@ -830,7 +839,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>24</v>
       </c>
@@ -838,7 +847,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>25</v>
       </c>
@@ -846,7 +855,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>26</v>
       </c>
@@ -854,7 +863,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>27</v>
       </c>
@@ -862,7 +871,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>28</v>
       </c>
@@ -870,7 +879,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>29</v>
       </c>
@@ -878,7 +887,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>30</v>
       </c>
@@ -886,7 +895,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>31</v>
       </c>
@@ -894,7 +903,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>32</v>
       </c>
@@ -902,7 +911,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>33</v>
       </c>
@@ -910,7 +919,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>34</v>
       </c>
@@ -918,7 +927,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>35</v>
       </c>
@@ -926,7 +935,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>36</v>
       </c>
@@ -934,7 +943,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>37</v>
       </c>
@@ -942,7 +951,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>38</v>
       </c>
@@ -950,7 +959,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>39</v>
       </c>
@@ -958,7 +967,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>40</v>
       </c>
@@ -966,7 +975,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>41</v>
       </c>
@@ -974,7 +983,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>42</v>
       </c>
@@ -982,7 +991,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>43</v>
       </c>
@@ -990,7 +999,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>44</v>
       </c>
@@ -998,7 +1007,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>45</v>
       </c>
@@ -1006,7 +1015,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>46</v>
       </c>
@@ -1014,7 +1023,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>47</v>
       </c>
@@ -1022,7 +1031,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>48</v>
       </c>
@@ -1030,7 +1039,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>49</v>
       </c>
@@ -1038,7 +1047,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>50</v>
       </c>
@@ -1046,7 +1055,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>51</v>
       </c>
@@ -1054,7 +1063,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>52</v>
       </c>
@@ -1062,7 +1071,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>53</v>
       </c>
@@ -1070,7 +1079,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>54</v>
       </c>
@@ -1078,7 +1087,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>55</v>
       </c>
@@ -1086,7 +1095,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>56</v>
       </c>
@@ -1094,7 +1103,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>57</v>
       </c>
@@ -1102,7 +1111,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>58</v>
       </c>
@@ -1110,7 +1119,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>59</v>
       </c>
@@ -1118,7 +1127,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>60</v>
       </c>
@@ -1126,7 +1135,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>61</v>
       </c>
@@ -1134,7 +1143,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>62</v>
       </c>
@@ -1142,7 +1151,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <v>63</v>
       </c>
@@ -1150,7 +1159,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <v>64</v>
       </c>
@@ -1158,7 +1167,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <v>65</v>
       </c>
@@ -1166,7 +1175,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
         <v>66</v>
       </c>
@@ -1174,7 +1183,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
         <v>67</v>
       </c>
@@ -1182,7 +1191,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
         <v>68</v>
       </c>
@@ -1190,7 +1199,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
         <v>69</v>
       </c>
@@ -1198,7 +1207,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
         <v>70</v>
       </c>
@@ -1206,7 +1215,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
         <v>71</v>
       </c>
@@ -1214,7 +1223,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
         <v>72</v>
       </c>
@@ -1222,7 +1231,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
         <v>73</v>
       </c>
@@ -1230,7 +1239,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
         <v>74</v>
       </c>
@@ -1238,7 +1247,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
         <v>75</v>
       </c>
@@ -1246,7 +1255,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="76" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
         <v>76</v>
       </c>
@@ -1254,7 +1263,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="77" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
         <v>77</v>
       </c>
@@ -1262,7 +1271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
         <v>78</v>
       </c>
@@ -1270,7 +1279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
         <v>79</v>
       </c>
@@ -1278,7 +1287,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="80" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
         <v>83</v>
       </c>
@@ -1286,7 +1295,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
         <v>86</v>
       </c>
@@ -1294,7 +1303,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
         <v>87</v>
       </c>
@@ -1302,7 +1311,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
         <v>89</v>
       </c>
@@ -1310,7 +1319,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="84" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
         <v>91</v>
       </c>
@@ -1318,12 +1327,36 @@
         <v>27</v>
       </c>
     </row>
-    <row r="85" spans="1:2" ht="20" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
         <v>92</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
+      <c r="A86" s="1">
+        <v>93</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
+      <c r="A87" s="1">
+        <v>94</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" ht="20.25" x14ac:dyDescent="0.35">
+      <c r="A88" s="1">
+        <v>95</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
